--- a/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>植物運送水分的是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>木質部</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>蒸散拉力</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>雙向</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>蒸散作用</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>水分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>植物運送養分的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>韌皮部</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>根莖葉</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>葉</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>養分</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>木質部運送方向？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>韌皮部</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>葉的氣孔</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>由根往上</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>向上</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>韌皮部可幾向運送？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>韌皮部</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>蒸散作用</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>根莖葉</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>雙向</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>雙向</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>木質部與韌皮部合稱？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>維管束</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>蒸散拉力</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>背面</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>系統</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>拉動水分向上的作用是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>蒸散作用</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>背面</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>根莖葉</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>拉力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>水分由葉的什麼散失？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>氣孔</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>葉</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>木質部</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>孔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>養分由哪裡製造後運送？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>雙向</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>韌皮部</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水與礦物質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>葉</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>光合</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>植物吸收水分主要靠哪個器官？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>根莖葉</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>根</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>韌皮部</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>雙向</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>氣孔主要分布在葉的哪一面？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>背面</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>葉背</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>木質部運送的物質？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>蒸散與吸水</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>水與礦物質</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>蒸散拉力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>水分</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>原料</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>韌皮部運送的物質？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>光合養分</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>木質部</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>葡萄糖</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>蒸散作用發生在？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>韌皮部</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>蒸散作用</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>葉的氣孔</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>水與礦物質</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>葉</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>維管束分布於？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>根莖葉</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>木質部</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>全株</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>植物缺水枯萎與什麼失衡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>蒸散與吸水</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>水與礦物質</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>果實變甜靠什麼運糖？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>蒸散與吸水</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>葉</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>韌皮部</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>運養</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>木質部運輸主要動力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>蒸散拉力</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>木質部</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>拉力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>養分能往下運到根嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>溶於水的礦物質</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>蒸散加快易缺水需調節氣孔</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>養分無法向下運輸影響根</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>能(韌皮部雙向)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>雙向</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>蒸散作用會使植物散失什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>維管束</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>木質部</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>失水</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>木質部除運水還運送什麼？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>溶於水的礦物質</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>蒸散加快易缺水需調節氣孔</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>根吸水經木質部靠蒸散拉力向上到葉</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>礦物質</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物3-1 植物體內的運輸　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明植物水分如何從根運到葉？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>木質部向上運水、韌皮部雙向運養</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>能(韌皮部雙向)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>養分無法運送到果實</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>根吸水經木質部靠蒸散拉力向上到葉</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較木質部與韌皮部運送方向與物質？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>能(韌皮部雙向)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>根吸水經木質部靠蒸散拉力向上到葉</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>木質部向上運水、韌皮部雙向運養</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>蒸散作用對植物的雙重影響？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>蒸散加快易缺水需調節氣孔</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>助水分上升但過度會失水枯萎</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>養分無法運送到果實</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>雙面</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>環割樹皮(去韌皮部)會如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>養分無法向下運輸影響根</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>木質部向上運水、韌皮部雙向運養</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>減少蒸散避免過度失水</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>維管束如何構成完整運輸系統？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>助水分上升但過度會失水枯萎</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>木質韌皮部連貫根莖葉運水運養</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>能(韌皮部雙向)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>減少蒸散避免過度失水</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>系統</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>乾熱環境對植物運輸的影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>能(韌皮部雙向)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>溶於水的礦物質</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>蒸散加快易缺水需調節氣孔</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>木質部向上運水、韌皮部雙向運養</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何說水分向上不需植物耗大量能量？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>都有專門管道運送物質</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>主要靠蒸散拉力被動上升</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>養分無法向下運輸影響根</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>被動</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>植物運輸與人體循環的相似處？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>養分無法運送到果實</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>主要靠蒸散拉力被動上升</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>都有專門管道運送物質</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>類比</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>炎熱正午植物氣孔常關閉的原因？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>木質韌皮部連貫根莖葉運水運養</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>木質部向上運水、韌皮部雙向運養</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>養分無法運送到果實</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>減少蒸散避免過度失水</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何砍斷莖的韌皮部果實難變甜？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>木質部向上運水、韌皮部雙向運養</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>助水分上升但過度會失水枯萎</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>養分無法運送到果實</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>溶於水的礦物質</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>運養</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>水分：木質部是植物體內專門運送水分和礦物質的管道，由根一路通到葉</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>養分</t>
+          <t>養分：韌皮部負責運送葉子行光合作用製造的養分，送到植物各部位</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>向上</t>
+          <t>向上：木質部把根吸收的水由下往上運送，靠蒸散作用產生的拉力</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>雙向：韌皮部運送養分時可以往上也可以往下，依植物需要而定</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>系統：木質部和韌皮部合起來組成維管束，是植物體內的運輸系統</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>拉力</t>
+          <t>拉力：葉片水分從氣孔蒸發散失，產生的拉力把水分往上拉</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>孔</t>
+          <t>氣孔：葉片表面有許多小孔叫氣孔，水分會從這裡蒸發散失到空氣中</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>光合</t>
+          <t>光合：葉片行光合作用製造出養分，再經韌皮部運送到全株</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>吸收：植物主要靠根部的根毛從土壤中吸收水分和溶於水中的礦物質</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>葉背</t>
+          <t>葉背：多數植物的氣孔主要分布在葉片背面，可以減少陽光直射造成的水分散失</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>原料</t>
+          <t>原料：木質部運送的是根部吸收的水分與溶在水中的礦物質</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>葡萄糖</t>
+          <t>葡萄糖：韌皮部運送的是葉子行光合作用製造出來的醣類等養分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>葉</t>
+          <t>葉：蒸散作用是水分從葉片表面的氣孔蒸發到空氣中的過程</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>全株</t>
+          <t>全株：維管束像血管一樣貫穿植物的根、莖、葉，負責運輸物質</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>水分：根部吸水跟不上葉片蒸散散失的速度時，植物就會缺水枯萎</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>運養</t>
+          <t>運養：葉片製造的醣類經韌皮部運送到果實，果實才會累積糖分變甜</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>拉力</t>
+          <t>拉力：木質部運水主要靠葉片蒸散作用產生的拉力，而非植物主動抽送</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>雙向：韌皮部運送養分能雙向進行，所以葉片養分能往下送到根部儲存</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>失水</t>
+          <t>失水：植物體內的水分經由氣孔以水蒸氣的形式散失到空氣中，這個過程稱為蒸散作用</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>礦物質</t>
+          <t>礦物質：木質部除了運輸水分，也一併運送溶解在水中的礦物質，從根部往上輸送到植物各部位</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：根吸收的水分進入木質部，靠葉片蒸散作用產生的拉力被拉往上到葉</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：木質部只能由下往上運水和礦物質，韌皮部則能雙向運送養分</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>雙面</t>
+          <t>雙面影響：蒸散能幫助水分往上運送，但天氣太乾熱時過度蒸散會讓植物枯萎</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗現象：環狀剝除樹皮會切斷韌皮部，養分無法往下運到根，根會受損</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>系統</t>
+          <t>系統連貫：木質部和韌皮部貫穿根莖葉，分別負責運水和運養，構成完整系統</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>環境影響：乾熱會使蒸散加快、水分散失變多，植物需調節氣孔開閉來因應</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>被動</t>
+          <t>被動運輸：水分向上主要靠蒸散作用產生的物理拉力被動上升，不需額外耗能</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>類比</t>
+          <t>類比相似：植物用維管束、人體用血管，都是靠專門管道系統運送需要的物質</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：正午氣溫高、蒸散作用旺盛，植物為了避免體內水分散失過多而缺水，會關閉部分氣孔來減少蒸散</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>運養</t>
+          <t>運養：韌皮部負責運送葉片行光合作用製造的養分（如醣類）到植物各處，若韌皮部被破壞，養分無法送達果實，果實就難以累積糖分變甜</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-1_三種難度測驗卷.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>韌皮部</t>
+          <t>木質部</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>氣孔</t>
+          <t>雙向</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>葉</t>
+          <t>韌皮部</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>維管束</t>
+          <t>水與礦物質</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>木質部</t>
+          <t>蒸散拉力</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>韌皮部</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>韌皮部</t>
+          <t>氣孔</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>水與礦物質</t>
+          <t>蒸散與吸水</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>根莖葉</t>
+          <t>維管束</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>雙向</t>
+          <t>氣孔</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>蒸散作用</t>
+          <t>蒸散與吸水</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>水與礦物質</t>
+          <t>木質部</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>由根往上</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>維管束</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>氣孔</t>
-        </is>
-      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>木質部</t>
+          <t>水與礦物質</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
